--- a/assets/constructions/examples/ctd_die_2.xlsx
+++ b/assets/constructions/examples/ctd_die_2.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL6"/>
+  <dimension ref="A1:AP6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -619,51 +619,63 @@
           <t>releasepack</t>
         </is>
       </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SCS 37040-4D</t>
+          <t>ZD03-43.0-XP40-WC08-02</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>PALBIT</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>JetDrills</t>
-        </is>
-      </c>
+          <t>LIKON</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>PALB_SP1104_H</t>
+          <t>ISO_WC0804_H</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Palbit</t>
+          <t>LIKON</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>SPKX 110408</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>SPKX 110408</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>WCM_080412</t>
+        </is>
+      </c>
       <c r="N2" t="n">
         <v>3</v>
       </c>
@@ -671,7 +683,7 @@
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="n">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr">
@@ -681,17 +693,17 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>PALB_SP1104H</t>
+          <t>ISO_WC0804H</t>
         </is>
       </c>
       <c r="V2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -704,13 +716,13 @@
       </c>
       <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr"/>
+      <c r="AD2" t="n">
+        <v>229</v>
+      </c>
       <c r="AE2" t="inlineStr"/>
-      <c r="AF2" t="n">
-        <v>188</v>
-      </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="inlineStr"/>
@@ -720,44 +732,58 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>2019/Palbit General Catalogue</t>
-        </is>
-      </c>
+          <t>2022/LIKON Инструментальный каталог</t>
+        </is>
+      </c>
+      <c r="AM2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ZD04-54.0-XP40-WC08-02</t>
+          <t>KSD-C32-24,5-183-W</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>LIKON</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
+          <t>DEREK</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>KSD-W</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>ISO_WC0804_H</t>
+          <t>WC0402H</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>LIKON</t>
+          <t>DEREK</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>54</v>
+        <v>24.5</v>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>WCMX040208</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>WCM_080412</t>
+          <t>WCMX040208</t>
         </is>
       </c>
       <c r="N3" t="n">
@@ -767,27 +793,27 @@
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="n">
-        <v>216</v>
+        <v>98</v>
       </c>
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr">
         <is>
-          <t>ISO_9766:40</t>
+          <t>ISO_9766:32</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>ISO_WC0804H</t>
+          <t>DER_WC0402H</t>
         </is>
       </c>
       <c r="V3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -796,64 +822,86 @@
       </c>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr"/>
+      <c r="AC3" t="n">
+        <v>0</v>
+      </c>
       <c r="AD3" t="n">
-        <v>316</v>
-      </c>
-      <c r="AE3" t="inlineStr"/>
-      <c r="AF3" t="inlineStr"/>
+        <v>183</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>183</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>123</v>
+      </c>
       <c r="AG3" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="inlineStr"/>
-      <c r="AJ3" t="inlineStr"/>
+      <c r="AJ3" t="n">
+        <v>0.68</v>
+      </c>
       <c r="AK3" t="n">
         <v>0</v>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>2022/LIKON Инструментальный каталог</t>
-        </is>
-      </c>
+          <t>2017/derek Металлорежущий инструмент и оснастка</t>
+        </is>
+      </c>
+      <c r="AM3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ZD03-24.5-XP25-WC04-02</t>
+          <t>KSD-C40-44-245-S</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>LIKON</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
+          <t>DEREK</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>KSD-S</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>ISO_WC0402_H</t>
+          <t>SP1405H</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>LIKON</t>
+          <t>DEREK</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>24.5</v>
+        <v>44</v>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>SPGT140512</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>WCM_040208</t>
+          <t>SPGT140512</t>
         </is>
       </c>
       <c r="N4" t="n">
@@ -863,27 +911,27 @@
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="n">
-        <v>73.5</v>
+        <v>132</v>
       </c>
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr">
         <is>
-          <t>ISO_9766:25</t>
+          <t>ISO_9766:40</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>ISO_WC0402H</t>
+          <t>DER_SP1405H</t>
         </is>
       </c>
       <c r="V4" t="n">
         <v>3</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -892,74 +940,84 @@
       </c>
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr"/>
+      <c r="AC4" t="n">
+        <v>0</v>
+      </c>
       <c r="AD4" t="n">
-        <v>152</v>
-      </c>
-      <c r="AE4" t="inlineStr"/>
-      <c r="AF4" t="inlineStr"/>
+        <v>245</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>245</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>175</v>
+      </c>
       <c r="AG4" t="n">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="inlineStr"/>
-      <c r="AJ4" t="inlineStr"/>
+      <c r="AJ4" t="n">
+        <v>1.81</v>
+      </c>
       <c r="AK4" t="n">
         <v>0</v>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>2022/LIKON Инструментальный каталог</t>
-        </is>
-      </c>
+          <t>2017/derek Металлорежущий инструмент и оснастка</t>
+        </is>
+      </c>
+      <c r="AM4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN4" t="inlineStr"/>
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>TDS 18525-3D</t>
+          <t>KSD-C40-560-3-W</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PALBIT</t>
+          <t>DEREK</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>JetDrills</t>
+          <t>KSD-W</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>PALB_WC0302_H</t>
+          <t>DER_WC0402_H</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Palbit</t>
+          <t>DEREK</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>18.5</v>
+        <v>56</v>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>WCKX 030204</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>WCKX 030204</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>WCMX080412</t>
+        </is>
+      </c>
       <c r="N5" t="n">
         <v>3</v>
       </c>
@@ -967,29 +1025,27 @@
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="n">
-        <v>55.5</v>
-      </c>
-      <c r="S5" t="n">
-        <v>3</v>
-      </c>
+        <v>168</v>
+      </c>
+      <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr">
         <is>
-          <t>ISO_9766:25</t>
+          <t>ISO_9766:40</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>PALB_WC0302H</t>
+          <t>DER_WC0402H</t>
         </is>
       </c>
       <c r="V5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="W5" t="n">
         <v>1</v>
       </c>
       <c r="X5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -998,34 +1054,52 @@
       </c>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="inlineStr"/>
+      <c r="AD5" t="n">
+        <v>274</v>
+      </c>
       <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="n">
-        <v>84</v>
+        <v>204</v>
       </c>
       <c r="AG5" t="n">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="inlineStr"/>
-      <c r="AJ5" t="inlineStr"/>
+      <c r="AJ5" t="n">
+        <v>2.79</v>
+      </c>
       <c r="AK5" t="n">
         <v>0</v>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>2019/Palbit General Catalogue</t>
-        </is>
+          <t>2019/DEREK2019.pdf</t>
+        </is>
+      </c>
+      <c r="AM5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>291.75</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="AP5" t="n">
+        <v>23915.89</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>KSD-C32-30-215-S</t>
+          <t>KSD-C32-240-4-W</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1035,13 +1109,13 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>KSD-S</t>
+          <t>KSD-W</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>SP0904H</t>
+          <t>DER_WC0804_H</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1050,20 +1124,16 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>SPGT090408</t>
-        </is>
-      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>SPGT090408</t>
+          <t>WCMX040208</t>
         </is>
       </c>
       <c r="N6" t="n">
@@ -1073,7 +1143,7 @@
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="n">
-        <v>120</v>
+        <v>96</v>
       </c>
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr">
@@ -1083,11 +1153,11 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>DER_SP0904H</t>
+          <t>DER_WC0804H</t>
         </is>
       </c>
       <c r="V6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="W6" t="n">
         <v>1</v>
@@ -1105,17 +1175,13 @@
         <v>32</v>
       </c>
       <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="n">
-        <v>0</v>
-      </c>
+      <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="n">
-        <v>215</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>215</v>
-      </c>
+        <v>187</v>
+      </c>
+      <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="n">
-        <v>155</v>
+        <v>127</v>
       </c>
       <c r="AG6" t="n">
         <v>60</v>
@@ -1123,15 +1189,29 @@
       <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="inlineStr"/>
       <c r="AJ6" t="n">
-        <v>0.87</v>
+        <v>0.67</v>
       </c>
       <c r="AK6" t="n">
         <v>0</v>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>2017/derek Металлорежущий инструмент и оснастка</t>
-        </is>
+          <t>2019/DEREK2019.pdf</t>
+        </is>
+      </c>
+      <c r="AM6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>145.89</v>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="AP6" t="n">
+        <v>11959.17</v>
       </c>
     </row>
   </sheetData>
